--- a/sample_templates/库存出入库流水.xlsx
+++ b/sample_templates/库存出入库流水.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -566,7 +566,7 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>报工</t>
+          <t>生产入库</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>报工</t>
+          <t>生产入库</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -625,33 +625,33 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>R82.205</t>
+          <t>JP-001</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>对位芳纶回收料-进口开松料</t>
+          <t>芳纶浆粕</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>原材料</t>
+          <t>产成品</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>原料仓</t>
+          <t>成品仓</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="n">
-        <v>5000</v>
+        <v>800</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
@@ -660,57 +660,10 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>领料出库</t>
+          <t>销售出库</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>浆粕车间</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-07-20</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>JP-001</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>芳纶浆粕</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>产成品</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>成品仓</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="n">
-        <v>800</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>千克</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>销售出库</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>浆粕车间</t>
         </is>
@@ -753,28 +706,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. 浆粕成品完工入库：业务类型填「报工」，单价金额留空，结算时按工单完工成本回填；工单号自动关联当月浆粕工单（PULP202607）。</t>
+          <t>2. 浆粕成品完工入库：业务类型填「生产入库」，单价/金额留空，结算时按工单完工成本自动回填；工单号自动关联当月浆粕工单（PULP202607）。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. 浆粕原料投料：业务类型填「领料出库」（对应投料记录），数量填正数，系统自动按出库处理。</t>
+          <t>3. 浆粕成品销售出库：业务类型填「销售出库」，单价/金额留空，结算时按月末加权价自动回填。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. 销售出库/采购入库等：业务类型按实际填（销售出库/采购入库/其它入库/库存调整）。</t>
+          <t>4. 其他业务（采购入库/其它入库/库存调整等）：业务类型按实际填；单价金额留空由系统回填。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. 方向由业务类型自动判断：报工/采购入库/其它入库=入库；领料出库/销售出库=出库。</t>
+          <t>5. 方向由业务类型自动判断：生产入库/采购入库/其它入库=入库；销售出库/领料出库=出库。</t>
         </is>
       </c>
     </row>
@@ -788,7 +741,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7. 浆粕成品入库也可用专用「浆粕成品入库」模板（只填成品入库行）。</t>
+          <t>7. 浆粕原料投料不走本模板：原料投料用「投料记录」（浆粕车间领料-投料记录）导入。</t>
         </is>
       </c>
     </row>

--- a/sample_templates/库存出入库流水.xlsx
+++ b/sample_templates/库存出入库流水.xlsx
@@ -455,7 +455,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -625,45 +625,92 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>JP-001</t>
+          <t>R82.205</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>芳纶浆粕</t>
+          <t>对位芳纶回收料-进口开松料</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>产成品</t>
+          <t>原材料</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr"/>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>成品仓</t>
+          <t>原料仓</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr"/>
       <c r="H4" s="2" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>千克</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>领料出库</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>浆粕车间</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-07-20</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>JP-001</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>芳纶浆粕</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>产成品</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>成品仓</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="n">
         <v>800</v>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>千克</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>销售出库</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>浆粕车间</t>
         </is>
@@ -683,7 +730,7 @@
   <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="118" customWidth="1" min="1" max="1"/>
+    <col width="120" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -706,42 +753,42 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. 浆粕成品完工入库：业务类型填「生产入库」，单价/金额留空，结算时按工单完工成本自动回填；工单号自动关联当月浆粕工单（PULP202607）。</t>
+          <t>2. 浆粕成品完工入库：业务类型填「生产入库」，单价/金额留空，结算时按工单完工成本自动回填。</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. 浆粕成品销售出库：业务类型填「销售出库」，单价/金额留空，结算时按月末加权价自动回填。</t>
+          <t>3. 浆粕原料投料：业务类型填「领料出库」（浆粕车间无生产工单，原料消耗直接走流水出库，不走投料记录），单价/金额留空，按月末加权价自动回填。</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. 其他业务（采购入库/其它入库/库存调整等）：业务类型按实际填；单价金额留空由系统回填。</t>
+          <t>4. 浆粕成品销售出库：业务类型填「销售出库」，单价/金额留空，按月末加权价自动回填。</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. 方向由业务类型自动判断：生产入库/采购入库/其它入库=入库；销售出库/领料出库=出库。</t>
+          <t>5. 其他业务（采购入库/其它入库/库存调整等）：业务类型按实际填；单价金额留空由系统回填。</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. 必填列：创建时间、物料编号、操作数量、业务类型；车间建议填（浆粕车间）。</t>
+          <t>6. 方向由业务类型自动判断：生产入库/采购入库/其它入库=入库；领料出库/销售出库=出库。</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>7. 浆粕原料投料不走本模板：原料投料用「投料记录」（浆粕车间领料-投料记录）导入。</t>
+          <t>7. 必填列：创建时间、物料编号、操作数量、业务类型；车间建议填（浆粕车间）。</t>
         </is>
       </c>
     </row>
